--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126270181</v>
+        <v>126270138</v>
       </c>
       <c r="B3" t="n">
-        <v>92528</v>
+        <v>78997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754046</v>
+        <v>753873</v>
       </c>
       <c r="R3" t="n">
-        <v>7232840</v>
+        <v>7232617</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,32 +885,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126270138</v>
+        <v>126270126</v>
       </c>
       <c r="B4" t="n">
-        <v>78997</v>
+        <v>79591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753873</v>
+        <v>754089</v>
       </c>
       <c r="R4" t="n">
-        <v>7232617</v>
+        <v>7232834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126270165</v>
+        <v>126270181</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754052</v>
+        <v>754046</v>
       </c>
       <c r="R5" t="n">
-        <v>7232732</v>
+        <v>7232840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126270126</v>
+        <v>126270165</v>
       </c>
       <c r="B6" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>754089</v>
+        <v>754052</v>
       </c>
       <c r="R6" t="n">
-        <v>7232834</v>
+        <v>7232732</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,45 +1188,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126270171</v>
+        <v>126270154</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>57756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754050</v>
+        <v>754057</v>
       </c>
       <c r="R7" t="n">
-        <v>7232814</v>
+        <v>7232729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1398,53 +1406,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126270154</v>
+        <v>126270171</v>
       </c>
       <c r="B9" t="n">
-        <v>57756</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754057</v>
+        <v>754050</v>
       </c>
       <c r="R9" t="n">
-        <v>7232729</v>
+        <v>7232814</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126270174</v>
+        <v>126270191</v>
       </c>
       <c r="B15" t="n">
-        <v>78640</v>
+        <v>92522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754019</v>
+        <v>754079</v>
       </c>
       <c r="R15" t="n">
-        <v>7232841</v>
+        <v>7232857</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126270191</v>
+        <v>126270148</v>
       </c>
       <c r="B16" t="n">
-        <v>92522</v>
+        <v>92720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754079</v>
+        <v>753884</v>
       </c>
       <c r="R16" t="n">
-        <v>7232857</v>
+        <v>7232663</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126270148</v>
+        <v>126270174</v>
       </c>
       <c r="B17" t="n">
-        <v>92720</v>
+        <v>78640</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,21 +2225,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753884</v>
+        <v>754019</v>
       </c>
       <c r="R17" t="n">
-        <v>7232663</v>
+        <v>7232841</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2416,32 +2416,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126270123</v>
+        <v>126270187</v>
       </c>
       <c r="B19" t="n">
-        <v>91203</v>
+        <v>77922</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753949</v>
+        <v>754065</v>
       </c>
       <c r="R19" t="n">
-        <v>7232720</v>
+        <v>7232758</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2517,32 +2517,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126270187</v>
+        <v>126270123</v>
       </c>
       <c r="B20" t="n">
-        <v>77922</v>
+        <v>91203</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754065</v>
+        <v>753949</v>
       </c>
       <c r="R20" t="n">
-        <v>7232758</v>
+        <v>7232720</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2719,49 +2719,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126270128</v>
+        <v>126270142</v>
       </c>
       <c r="B22" t="n">
-        <v>56844</v>
+        <v>92720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753884</v>
+        <v>753986</v>
       </c>
       <c r="R22" t="n">
-        <v>7232589</v>
+        <v>7232809</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2794,11 +2790,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillningshög</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2930,45 +2921,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126270142</v>
+        <v>126270128</v>
       </c>
       <c r="B24" t="n">
-        <v>92720</v>
+        <v>56844</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753986</v>
+        <v>753884</v>
       </c>
       <c r="R24" t="n">
-        <v>7232809</v>
+        <v>7232589</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3001,6 +2996,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spillningshög</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3031,7 +3031,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126270139</v>
+        <v>126270140</v>
       </c>
       <c r="B25" t="n">
         <v>92720</v>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754049</v>
+        <v>754099</v>
       </c>
       <c r="R25" t="n">
-        <v>7232811</v>
+        <v>7232830</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,32 +3132,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126270137</v>
+        <v>126270139</v>
       </c>
       <c r="B26" t="n">
-        <v>78997</v>
+        <v>92720</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6434</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754063</v>
+        <v>754049</v>
       </c>
       <c r="R26" t="n">
-        <v>7232755</v>
+        <v>7232811</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,32 +3233,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126270184</v>
+        <v>126270146</v>
       </c>
       <c r="B27" t="n">
-        <v>92528</v>
+        <v>92720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753906</v>
+        <v>753928</v>
       </c>
       <c r="R27" t="n">
-        <v>7232656</v>
+        <v>7232730</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126270140</v>
+        <v>126270173</v>
       </c>
       <c r="B28" t="n">
-        <v>92720</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>754099</v>
+        <v>753873</v>
       </c>
       <c r="R28" t="n">
-        <v>7232830</v>
+        <v>7232617</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,32 +3435,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126270146</v>
+        <v>126270137</v>
       </c>
       <c r="B29" t="n">
-        <v>92720</v>
+        <v>78997</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753928</v>
+        <v>754063</v>
       </c>
       <c r="R29" t="n">
-        <v>7232730</v>
+        <v>7232755</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,32 +3536,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126270173</v>
+        <v>126270184</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753873</v>
+        <v>753906</v>
       </c>
       <c r="R30" t="n">
-        <v>7232617</v>
+        <v>7232656</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3637,32 +3637,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126270176</v>
+        <v>126270182</v>
       </c>
       <c r="B31" t="n">
-        <v>78640</v>
+        <v>92528</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753946</v>
+        <v>753991</v>
       </c>
       <c r="R31" t="n">
-        <v>7232791</v>
+        <v>7232817</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3738,32 +3738,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126270182</v>
+        <v>126270186</v>
       </c>
       <c r="B32" t="n">
-        <v>92528</v>
+        <v>77922</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753991</v>
+        <v>754028</v>
       </c>
       <c r="R32" t="n">
-        <v>7232817</v>
+        <v>7232689</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126270186</v>
+        <v>126270176</v>
       </c>
       <c r="B33" t="n">
-        <v>77922</v>
+        <v>78640</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>754028</v>
+        <v>753946</v>
       </c>
       <c r="R33" t="n">
-        <v>7232689</v>
+        <v>7232791</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4041,32 +4041,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126270180</v>
+        <v>126270124</v>
       </c>
       <c r="B35" t="n">
-        <v>92528</v>
+        <v>79591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>754036</v>
+        <v>754057</v>
       </c>
       <c r="R35" t="n">
-        <v>7232745</v>
+        <v>7232734</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4142,32 +4142,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126270124</v>
+        <v>126270180</v>
       </c>
       <c r="B36" t="n">
-        <v>79591</v>
+        <v>92528</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>754057</v>
+        <v>754036</v>
       </c>
       <c r="R36" t="n">
-        <v>7232734</v>
+        <v>7232745</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,32 +4243,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126270122</v>
+        <v>126270197</v>
       </c>
       <c r="B37" t="n">
-        <v>91203</v>
+        <v>78379</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>754070</v>
+        <v>754065</v>
       </c>
       <c r="R37" t="n">
-        <v>7232862</v>
+        <v>7232758</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4344,32 +4344,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126270197</v>
+        <v>126270122</v>
       </c>
       <c r="B38" t="n">
-        <v>78379</v>
+        <v>91203</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>754065</v>
+        <v>754070</v>
       </c>
       <c r="R38" t="n">
-        <v>7232758</v>
+        <v>7232862</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126270169</v>
+        <v>126270130</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>91188</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,21 +4869,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>754075</v>
+        <v>753974</v>
       </c>
       <c r="R43" t="n">
-        <v>7232767</v>
+        <v>7232782</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4929,11 +4929,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4964,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126270130</v>
+        <v>126270169</v>
       </c>
       <c r="B44" t="n">
-        <v>91188</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4975,21 +4970,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4994,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753974</v>
+        <v>754075</v>
       </c>
       <c r="R44" t="n">
-        <v>7232782</v>
+        <v>7232767</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5035,6 +5030,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5065,10 +5065,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126270167</v>
+        <v>126270157</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5076,21 +5076,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>754064</v>
+        <v>754037</v>
       </c>
       <c r="R45" t="n">
-        <v>7232752</v>
+        <v>7232824</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126270157</v>
+        <v>126270167</v>
       </c>
       <c r="B46" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5177,21 +5177,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>754037</v>
+        <v>754064</v>
       </c>
       <c r="R46" t="n">
-        <v>7232824</v>
+        <v>7232752</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5469,32 +5469,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126270175</v>
+        <v>126270155</v>
       </c>
       <c r="B49" t="n">
-        <v>78640</v>
+        <v>91166</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>2013</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753911</v>
+        <v>753884</v>
       </c>
       <c r="R49" t="n">
-        <v>7232730</v>
+        <v>7232663</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5548,6 +5548,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5570,32 +5571,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126270155</v>
+        <v>126270175</v>
       </c>
       <c r="B50" t="n">
-        <v>91166</v>
+        <v>78640</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2013</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5605,10 +5606,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753884</v>
+        <v>753911</v>
       </c>
       <c r="R50" t="n">
-        <v>7232663</v>
+        <v>7232730</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5649,7 +5650,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -885,32 +885,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126270126</v>
+        <v>126270181</v>
       </c>
       <c r="B4" t="n">
-        <v>79591</v>
+        <v>92528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754089</v>
+        <v>754046</v>
       </c>
       <c r="R4" t="n">
-        <v>7232834</v>
+        <v>7232840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126270181</v>
+        <v>126270165</v>
       </c>
       <c r="B5" t="n">
-        <v>92528</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754046</v>
+        <v>754052</v>
       </c>
       <c r="R5" t="n">
-        <v>7232840</v>
+        <v>7232732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126270165</v>
+        <v>126270126</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>754052</v>
+        <v>754089</v>
       </c>
       <c r="R6" t="n">
-        <v>7232732</v>
+        <v>7232834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,53 +1188,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126270154</v>
+        <v>126270171</v>
       </c>
       <c r="B7" t="n">
-        <v>57756</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754057</v>
+        <v>754050</v>
       </c>
       <c r="R7" t="n">
-        <v>7232729</v>
+        <v>7232814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1289,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126270151</v>
+        <v>126270154</v>
       </c>
       <c r="B8" t="n">
         <v>57756</v>
@@ -1340,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754019</v>
+        <v>754057</v>
       </c>
       <c r="R8" t="n">
-        <v>7232699</v>
+        <v>7232729</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,45 +1398,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126270171</v>
+        <v>126270151</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>57756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754050</v>
+        <v>754019</v>
       </c>
       <c r="R9" t="n">
-        <v>7232814</v>
+        <v>7232699</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126270140</v>
+        <v>126270173</v>
       </c>
       <c r="B25" t="n">
-        <v>92720</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754099</v>
+        <v>753873</v>
       </c>
       <c r="R25" t="n">
-        <v>7232830</v>
+        <v>7232617</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,32 +3132,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126270139</v>
+        <v>126270137</v>
       </c>
       <c r="B26" t="n">
-        <v>92720</v>
+        <v>78997</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754049</v>
+        <v>754063</v>
       </c>
       <c r="R26" t="n">
-        <v>7232811</v>
+        <v>7232755</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,32 +3233,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126270146</v>
+        <v>126270184</v>
       </c>
       <c r="B27" t="n">
-        <v>92720</v>
+        <v>92528</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753928</v>
+        <v>753906</v>
       </c>
       <c r="R27" t="n">
-        <v>7232730</v>
+        <v>7232656</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126270173</v>
+        <v>126270140</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>92720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753873</v>
+        <v>754099</v>
       </c>
       <c r="R28" t="n">
-        <v>7232617</v>
+        <v>7232830</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,32 +3435,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126270137</v>
+        <v>126270139</v>
       </c>
       <c r="B29" t="n">
-        <v>78997</v>
+        <v>92720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>754063</v>
+        <v>754049</v>
       </c>
       <c r="R29" t="n">
-        <v>7232755</v>
+        <v>7232811</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,32 +3536,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126270184</v>
+        <v>126270146</v>
       </c>
       <c r="B30" t="n">
-        <v>92528</v>
+        <v>92720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753906</v>
+        <v>753928</v>
       </c>
       <c r="R30" t="n">
-        <v>7232656</v>
+        <v>7232730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3637,32 +3637,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126270182</v>
+        <v>126270176</v>
       </c>
       <c r="B31" t="n">
-        <v>92528</v>
+        <v>78640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753991</v>
+        <v>753946</v>
       </c>
       <c r="R31" t="n">
-        <v>7232817</v>
+        <v>7232791</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3738,10 +3738,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126270186</v>
+        <v>126270143</v>
       </c>
       <c r="B32" t="n">
-        <v>77922</v>
+        <v>92720</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3749,21 +3749,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>754028</v>
+        <v>753997</v>
       </c>
       <c r="R32" t="n">
-        <v>7232689</v>
+        <v>7232748</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126270176</v>
+        <v>126270186</v>
       </c>
       <c r="B33" t="n">
-        <v>78640</v>
+        <v>77922</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753946</v>
+        <v>754028</v>
       </c>
       <c r="R33" t="n">
-        <v>7232791</v>
+        <v>7232689</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,32 +3940,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126270143</v>
+        <v>126270182</v>
       </c>
       <c r="B34" t="n">
-        <v>92720</v>
+        <v>92528</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753997</v>
+        <v>753991</v>
       </c>
       <c r="R34" t="n">
-        <v>7232748</v>
+        <v>7232817</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4445,10 +4445,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126270125</v>
+        <v>126270190</v>
       </c>
       <c r="B39" t="n">
-        <v>79591</v>
+        <v>77922</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4456,21 +4456,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>754064</v>
+        <v>754038</v>
       </c>
       <c r="R39" t="n">
-        <v>7232750</v>
+        <v>7232823</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4546,10 +4546,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126270190</v>
+        <v>126270125</v>
       </c>
       <c r="B40" t="n">
-        <v>77922</v>
+        <v>79591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4557,21 +4557,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>754038</v>
+        <v>754064</v>
       </c>
       <c r="R40" t="n">
-        <v>7232823</v>
+        <v>7232750</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126270130</v>
+        <v>126270145</v>
       </c>
       <c r="B43" t="n">
-        <v>91188</v>
+        <v>92720</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,21 +4869,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>112</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753974</v>
+        <v>753910</v>
       </c>
       <c r="R43" t="n">
-        <v>7232782</v>
+        <v>7232666</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126270169</v>
+        <v>126270130</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>91188</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4970,21 +4970,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>754075</v>
+        <v>753974</v>
       </c>
       <c r="R44" t="n">
-        <v>7232767</v>
+        <v>7232782</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5030,11 +5030,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5065,10 +5060,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126270157</v>
+        <v>126270169</v>
       </c>
       <c r="B45" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5076,21 +5071,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5100,10 +5095,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>754037</v>
+        <v>754075</v>
       </c>
       <c r="R45" t="n">
-        <v>7232824</v>
+        <v>7232767</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5136,6 +5131,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5166,10 +5166,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126270167</v>
+        <v>126270157</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5177,21 +5177,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>754064</v>
+        <v>754037</v>
       </c>
       <c r="R46" t="n">
-        <v>7232752</v>
+        <v>7232824</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5267,10 +5267,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126270145</v>
+        <v>126270167</v>
       </c>
       <c r="B47" t="n">
-        <v>92720</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5278,21 +5278,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753910</v>
+        <v>754064</v>
       </c>
       <c r="R47" t="n">
-        <v>7232666</v>
+        <v>7232752</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126270152</v>
       </c>
       <c r="B2" t="n">
-        <v>57756</v>
+        <v>57760</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126270138</v>
+        <v>126270181</v>
       </c>
       <c r="B3" t="n">
-        <v>78997</v>
+        <v>92532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753873</v>
+        <v>754046</v>
       </c>
       <c r="R3" t="n">
-        <v>7232617</v>
+        <v>7232840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126270181</v>
+        <v>126270138</v>
       </c>
       <c r="B4" t="n">
-        <v>92528</v>
+        <v>79001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754046</v>
+        <v>753873</v>
       </c>
       <c r="R4" t="n">
-        <v>7232840</v>
+        <v>7232617</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
         <v>126270165</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>126270126</v>
       </c>
       <c r="B6" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,45 +1188,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126270171</v>
+        <v>126270154</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>57760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754050</v>
+        <v>754057</v>
       </c>
       <c r="R7" t="n">
-        <v>7232814</v>
+        <v>7232729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126270154</v>
+        <v>126270151</v>
       </c>
       <c r="B8" t="n">
-        <v>57756</v>
+        <v>57760</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754057</v>
+        <v>754019</v>
       </c>
       <c r="R8" t="n">
-        <v>7232729</v>
+        <v>7232699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,53 +1406,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126270151</v>
+        <v>126270171</v>
       </c>
       <c r="B9" t="n">
-        <v>57756</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754019</v>
+        <v>754050</v>
       </c>
       <c r="R9" t="n">
-        <v>7232699</v>
+        <v>7232814</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,32 +1507,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126270149</v>
+        <v>126270172</v>
       </c>
       <c r="B10" t="n">
-        <v>80112</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753849</v>
+        <v>754070</v>
       </c>
       <c r="R10" t="n">
-        <v>7232635</v>
+        <v>7232862</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,32 +1608,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126270172</v>
+        <v>126270149</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>80116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>754070</v>
+        <v>753849</v>
       </c>
       <c r="R11" t="n">
-        <v>7232862</v>
+        <v>7232635</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,7 +1712,7 @@
         <v>126270141</v>
       </c>
       <c r="B12" t="n">
-        <v>92720</v>
+        <v>92724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>126270193</v>
       </c>
       <c r="B13" t="n">
-        <v>92522</v>
+        <v>92526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>126270194</v>
       </c>
       <c r="B14" t="n">
-        <v>92522</v>
+        <v>92526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126270191</v>
+        <v>126270174</v>
       </c>
       <c r="B15" t="n">
-        <v>92522</v>
+        <v>78644</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754079</v>
+        <v>754019</v>
       </c>
       <c r="R15" t="n">
-        <v>7232857</v>
+        <v>7232841</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,7 +2116,7 @@
         <v>126270148</v>
       </c>
       <c r="B16" t="n">
-        <v>92720</v>
+        <v>92724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126270174</v>
+        <v>126270191</v>
       </c>
       <c r="B17" t="n">
-        <v>78640</v>
+        <v>92526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,21 +2225,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754019</v>
+        <v>754079</v>
       </c>
       <c r="R17" t="n">
-        <v>7232841</v>
+        <v>7232857</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2318,7 +2318,7 @@
         <v>126270196</v>
       </c>
       <c r="B18" t="n">
-        <v>92522</v>
+        <v>92526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2416,32 +2416,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126270187</v>
+        <v>126270123</v>
       </c>
       <c r="B19" t="n">
-        <v>77922</v>
+        <v>91207</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754065</v>
+        <v>753949</v>
       </c>
       <c r="R19" t="n">
-        <v>7232758</v>
+        <v>7232720</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2517,32 +2517,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126270123</v>
+        <v>126270187</v>
       </c>
       <c r="B20" t="n">
-        <v>91203</v>
+        <v>77926</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753949</v>
+        <v>754065</v>
       </c>
       <c r="R20" t="n">
-        <v>7232720</v>
+        <v>7232758</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126270129</v>
+        <v>126270142</v>
       </c>
       <c r="B21" t="n">
-        <v>57812</v>
+        <v>92724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753902</v>
+        <v>753986</v>
       </c>
       <c r="R21" t="n">
-        <v>7232615</v>
+        <v>7232809</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,32 +2719,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126270142</v>
+        <v>126270183</v>
       </c>
       <c r="B22" t="n">
-        <v>92720</v>
+        <v>92532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753986</v>
+        <v>753979</v>
       </c>
       <c r="R22" t="n">
-        <v>7232809</v>
+        <v>7232812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126270183</v>
+        <v>126270128</v>
       </c>
       <c r="B23" t="n">
-        <v>92528</v>
+        <v>56848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2831,34 +2831,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753979</v>
+        <v>753884</v>
       </c>
       <c r="R23" t="n">
-        <v>7232812</v>
+        <v>7232589</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2891,6 +2895,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spillningshög</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2921,49 +2930,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126270128</v>
+        <v>126270129</v>
       </c>
       <c r="B24" t="n">
-        <v>56844</v>
+        <v>57816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753884</v>
+        <v>753902</v>
       </c>
       <c r="R24" t="n">
-        <v>7232589</v>
+        <v>7232615</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,11 +3001,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spillningshög</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126270173</v>
+        <v>126270140</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>92724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753873</v>
+        <v>754099</v>
       </c>
       <c r="R25" t="n">
-        <v>7232617</v>
+        <v>7232830</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,32 +3132,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126270137</v>
+        <v>126270139</v>
       </c>
       <c r="B26" t="n">
-        <v>78997</v>
+        <v>92724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6434</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754063</v>
+        <v>754049</v>
       </c>
       <c r="R26" t="n">
-        <v>7232755</v>
+        <v>7232811</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,32 +3233,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126270184</v>
+        <v>126270146</v>
       </c>
       <c r="B27" t="n">
-        <v>92528</v>
+        <v>92724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753906</v>
+        <v>753928</v>
       </c>
       <c r="R27" t="n">
-        <v>7232656</v>
+        <v>7232730</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126270140</v>
+        <v>126270173</v>
       </c>
       <c r="B28" t="n">
-        <v>92720</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>754099</v>
+        <v>753873</v>
       </c>
       <c r="R28" t="n">
-        <v>7232830</v>
+        <v>7232617</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,32 +3435,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126270139</v>
+        <v>126270137</v>
       </c>
       <c r="B29" t="n">
-        <v>92720</v>
+        <v>79001</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>754049</v>
+        <v>754063</v>
       </c>
       <c r="R29" t="n">
-        <v>7232811</v>
+        <v>7232755</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,32 +3536,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126270146</v>
+        <v>126270184</v>
       </c>
       <c r="B30" t="n">
-        <v>92720</v>
+        <v>92532</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753928</v>
+        <v>753906</v>
       </c>
       <c r="R30" t="n">
-        <v>7232730</v>
+        <v>7232656</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3640,7 +3640,7 @@
         <v>126270176</v>
       </c>
       <c r="B31" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>126270143</v>
       </c>
       <c r="B32" t="n">
-        <v>92720</v>
+        <v>92724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>126270186</v>
       </c>
       <c r="B33" t="n">
-        <v>77922</v>
+        <v>77926</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>126270182</v>
       </c>
       <c r="B34" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4041,32 +4041,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126270124</v>
+        <v>126270180</v>
       </c>
       <c r="B35" t="n">
-        <v>79591</v>
+        <v>92532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>754057</v>
+        <v>754036</v>
       </c>
       <c r="R35" t="n">
-        <v>7232734</v>
+        <v>7232745</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4142,32 +4142,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126270180</v>
+        <v>126270124</v>
       </c>
       <c r="B36" t="n">
-        <v>92528</v>
+        <v>79595</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>754036</v>
+        <v>754057</v>
       </c>
       <c r="R36" t="n">
-        <v>7232745</v>
+        <v>7232734</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,32 +4243,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126270197</v>
+        <v>126270122</v>
       </c>
       <c r="B37" t="n">
-        <v>78379</v>
+        <v>91207</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>754065</v>
+        <v>754070</v>
       </c>
       <c r="R37" t="n">
-        <v>7232758</v>
+        <v>7232862</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4344,32 +4344,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126270122</v>
+        <v>126270197</v>
       </c>
       <c r="B38" t="n">
-        <v>91203</v>
+        <v>78383</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>754070</v>
+        <v>754065</v>
       </c>
       <c r="R38" t="n">
-        <v>7232862</v>
+        <v>7232758</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4448,7 +4448,7 @@
         <v>126270190</v>
       </c>
       <c r="B39" t="n">
-        <v>77922</v>
+        <v>77926</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>126270125</v>
       </c>
       <c r="B40" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>126270127</v>
       </c>
       <c r="B41" t="n">
-        <v>91523</v>
+        <v>91527</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>126270170</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126270145</v>
+        <v>126270169</v>
       </c>
       <c r="B43" t="n">
-        <v>92720</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,21 +4869,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753910</v>
+        <v>754075</v>
       </c>
       <c r="R43" t="n">
-        <v>7232666</v>
+        <v>7232767</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4929,6 +4929,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4959,10 +4964,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126270130</v>
+        <v>126270157</v>
       </c>
       <c r="B44" t="n">
-        <v>91188</v>
+        <v>78735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4970,21 +4975,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4994,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753974</v>
+        <v>754037</v>
       </c>
       <c r="R44" t="n">
-        <v>7232782</v>
+        <v>7232824</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5060,10 +5065,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126270169</v>
+        <v>126270167</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5095,10 +5100,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>754075</v>
+        <v>754064</v>
       </c>
       <c r="R45" t="n">
-        <v>7232767</v>
+        <v>7232752</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5131,11 +5136,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5166,10 +5166,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126270157</v>
+        <v>126270130</v>
       </c>
       <c r="B46" t="n">
-        <v>78731</v>
+        <v>91192</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5177,21 +5177,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>112</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>754037</v>
+        <v>753974</v>
       </c>
       <c r="R46" t="n">
-        <v>7232824</v>
+        <v>7232782</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5267,10 +5267,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126270167</v>
+        <v>126270145</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>92724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5278,21 +5278,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>754064</v>
+        <v>753910</v>
       </c>
       <c r="R47" t="n">
-        <v>7232752</v>
+        <v>7232666</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5368,10 +5368,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126270144</v>
+        <v>126270175</v>
       </c>
       <c r="B48" t="n">
-        <v>92720</v>
+        <v>78644</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5379,21 +5379,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753928</v>
+        <v>753911</v>
       </c>
       <c r="R48" t="n">
-        <v>7232737</v>
+        <v>7232730</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,32 +5469,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126270155</v>
+        <v>126270144</v>
       </c>
       <c r="B49" t="n">
-        <v>91166</v>
+        <v>92724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2013</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753884</v>
+        <v>753928</v>
       </c>
       <c r="R49" t="n">
-        <v>7232663</v>
+        <v>7232737</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5548,7 +5548,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5571,32 +5570,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126270175</v>
+        <v>126270155</v>
       </c>
       <c r="B50" t="n">
-        <v>78640</v>
+        <v>91170</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>2013</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5606,10 +5605,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753911</v>
+        <v>753884</v>
       </c>
       <c r="R50" t="n">
-        <v>7232730</v>
+        <v>7232663</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,6 +5649,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -1188,53 +1188,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126270154</v>
+        <v>126270171</v>
       </c>
       <c r="B7" t="n">
-        <v>57760</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754057</v>
+        <v>754050</v>
       </c>
       <c r="R7" t="n">
-        <v>7232729</v>
+        <v>7232814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1289,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126270151</v>
+        <v>126270154</v>
       </c>
       <c r="B8" t="n">
         <v>57760</v>
@@ -1340,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754019</v>
+        <v>754057</v>
       </c>
       <c r="R8" t="n">
-        <v>7232699</v>
+        <v>7232729</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,45 +1398,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126270171</v>
+        <v>126270151</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>57760</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754050</v>
+        <v>754019</v>
       </c>
       <c r="R9" t="n">
-        <v>7232814</v>
+        <v>7232699</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -4647,48 +4647,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126270127</v>
+        <v>126270170</v>
       </c>
       <c r="B41" t="n">
-        <v>91527</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>71</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753997</v>
+        <v>754078</v>
       </c>
       <c r="R41" t="n">
-        <v>7232748</v>
+        <v>7232778</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4723,18 +4720,12 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Blev lätt till pulver när den rullades mellan fingrarna. Växte på den ännu stenhårda kärnveden inuti lågan</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4757,45 +4748,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126270170</v>
+        <v>126270127</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>91527</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>71</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>754078</v>
+        <v>753997</v>
       </c>
       <c r="R42" t="n">
-        <v>7232778</v>
+        <v>7232748</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4830,12 +4824,18 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Blev lätt till pulver när den rullades mellan fingrarna. Växte på den ännu stenhårda kärnveden inuti lågan</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126270169</v>
+        <v>126270145</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,21 +4869,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>754075</v>
+        <v>753910</v>
       </c>
       <c r="R43" t="n">
-        <v>7232767</v>
+        <v>7232666</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4929,11 +4929,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4964,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126270157</v>
+        <v>126270169</v>
       </c>
       <c r="B44" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4975,21 +4970,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4994,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>754037</v>
+        <v>754075</v>
       </c>
       <c r="R44" t="n">
-        <v>7232824</v>
+        <v>7232767</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5035,6 +5030,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5065,10 +5065,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126270167</v>
+        <v>126270157</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5076,21 +5076,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>754064</v>
+        <v>754037</v>
       </c>
       <c r="R45" t="n">
-        <v>7232752</v>
+        <v>7232824</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126270130</v>
+        <v>126270167</v>
       </c>
       <c r="B46" t="n">
-        <v>91192</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5177,21 +5177,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753974</v>
+        <v>754064</v>
       </c>
       <c r="R46" t="n">
-        <v>7232782</v>
+        <v>7232752</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5267,10 +5267,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126270145</v>
+        <v>126270130</v>
       </c>
       <c r="B47" t="n">
-        <v>92724</v>
+        <v>91192</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5278,21 +5278,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>112</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753910</v>
+        <v>753974</v>
       </c>
       <c r="R47" t="n">
-        <v>7232666</v>
+        <v>7232782</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126270181</v>
+        <v>126270138</v>
       </c>
       <c r="B3" t="n">
-        <v>92532</v>
+        <v>79001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754046</v>
+        <v>753873</v>
       </c>
       <c r="R3" t="n">
-        <v>7232840</v>
+        <v>7232617</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126270138</v>
+        <v>126270181</v>
       </c>
       <c r="B4" t="n">
-        <v>79001</v>
+        <v>92532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753873</v>
+        <v>754046</v>
       </c>
       <c r="R4" t="n">
-        <v>7232617</v>
+        <v>7232840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126270140</v>
+        <v>126270173</v>
       </c>
       <c r="B25" t="n">
-        <v>92724</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754099</v>
+        <v>753873</v>
       </c>
       <c r="R25" t="n">
-        <v>7232830</v>
+        <v>7232617</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126270139</v>
+        <v>126270140</v>
       </c>
       <c r="B26" t="n">
         <v>92724</v>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754049</v>
+        <v>754099</v>
       </c>
       <c r="R26" t="n">
-        <v>7232811</v>
+        <v>7232830</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,32 +3233,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126270146</v>
+        <v>126270137</v>
       </c>
       <c r="B27" t="n">
-        <v>92724</v>
+        <v>79001</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753928</v>
+        <v>754063</v>
       </c>
       <c r="R27" t="n">
-        <v>7232730</v>
+        <v>7232755</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3334,32 +3334,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126270173</v>
+        <v>126270184</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753873</v>
+        <v>753906</v>
       </c>
       <c r="R28" t="n">
-        <v>7232617</v>
+        <v>7232656</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,32 +3435,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126270137</v>
+        <v>126270139</v>
       </c>
       <c r="B29" t="n">
-        <v>79001</v>
+        <v>92724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>754063</v>
+        <v>754049</v>
       </c>
       <c r="R29" t="n">
-        <v>7232755</v>
+        <v>7232811</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,32 +3536,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126270184</v>
+        <v>126270146</v>
       </c>
       <c r="B30" t="n">
-        <v>92532</v>
+        <v>92724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753906</v>
+        <v>753928</v>
       </c>
       <c r="R30" t="n">
-        <v>7232656</v>
+        <v>7232730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4041,32 +4041,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126270180</v>
+        <v>126270124</v>
       </c>
       <c r="B35" t="n">
-        <v>92532</v>
+        <v>79595</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>754036</v>
+        <v>754057</v>
       </c>
       <c r="R35" t="n">
-        <v>7232745</v>
+        <v>7232734</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4142,32 +4142,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126270124</v>
+        <v>126270180</v>
       </c>
       <c r="B36" t="n">
-        <v>79595</v>
+        <v>92532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>754057</v>
+        <v>754036</v>
       </c>
       <c r="R36" t="n">
-        <v>7232734</v>
+        <v>7232745</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,32 +4243,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126270122</v>
+        <v>126270197</v>
       </c>
       <c r="B37" t="n">
-        <v>91207</v>
+        <v>78383</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>754070</v>
+        <v>754065</v>
       </c>
       <c r="R37" t="n">
-        <v>7232862</v>
+        <v>7232758</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4344,32 +4344,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126270197</v>
+        <v>126270122</v>
       </c>
       <c r="B38" t="n">
-        <v>78383</v>
+        <v>91207</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>754065</v>
+        <v>754070</v>
       </c>
       <c r="R38" t="n">
-        <v>7232758</v>
+        <v>7232862</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4748,48 +4748,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126270127</v>
+        <v>126270130</v>
       </c>
       <c r="B42" t="n">
-        <v>91527</v>
+        <v>91192</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753997</v>
+        <v>753974</v>
       </c>
       <c r="R42" t="n">
-        <v>7232748</v>
+        <v>7232782</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4824,18 +4821,12 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Blev lätt till pulver när den rullades mellan fingrarna. Växte på den ännu stenhårda kärnveden inuti lågan</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4858,10 +4849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126270145</v>
+        <v>126270169</v>
       </c>
       <c r="B43" t="n">
-        <v>92724</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,21 +4860,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4893,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753910</v>
+        <v>754075</v>
       </c>
       <c r="R43" t="n">
-        <v>7232666</v>
+        <v>7232767</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4929,6 +4920,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4959,10 +4955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126270169</v>
+        <v>126270145</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4970,21 +4966,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4994,10 +4990,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>754075</v>
+        <v>753910</v>
       </c>
       <c r="R44" t="n">
-        <v>7232767</v>
+        <v>7232666</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5030,11 +5026,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5267,10 +5258,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126270130</v>
+        <v>126270175</v>
       </c>
       <c r="B47" t="n">
-        <v>91192</v>
+        <v>78644</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5278,21 +5269,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5302,10 +5293,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753974</v>
+        <v>753911</v>
       </c>
       <c r="R47" t="n">
-        <v>7232782</v>
+        <v>7232730</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5368,10 +5359,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126270175</v>
+        <v>126270144</v>
       </c>
       <c r="B48" t="n">
-        <v>78644</v>
+        <v>92724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5379,21 +5370,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5403,10 +5394,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753911</v>
+        <v>753928</v>
       </c>
       <c r="R48" t="n">
-        <v>7232730</v>
+        <v>7232737</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,32 +5460,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126270144</v>
+        <v>126270155</v>
       </c>
       <c r="B49" t="n">
-        <v>92724</v>
+        <v>91170</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>2013</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5504,10 +5495,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753928</v>
+        <v>753884</v>
       </c>
       <c r="R49" t="n">
-        <v>7232737</v>
+        <v>7232663</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5548,6 +5539,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5570,10 +5562,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126270155</v>
+        <v>126270127</v>
       </c>
       <c r="B50" t="n">
-        <v>91170</v>
+        <v>91527</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5581,34 +5573,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2013</v>
+        <v>71</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753884</v>
+        <v>753997</v>
       </c>
       <c r="R50" t="n">
-        <v>7232663</v>
+        <v>7232748</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5641,6 +5636,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Blev lätt till pulver när den rullades mellan fingrarna. Växte på den ännu stenhårda kärnveden inuti lågan, satt fast rätt ordentligt i underlaget. Tjock och "bullig", med porer hela vägen till kanten</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -2618,45 +2618,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126270142</v>
+        <v>126270128</v>
       </c>
       <c r="B21" t="n">
-        <v>92724</v>
+        <v>56848</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753986</v>
+        <v>753884</v>
       </c>
       <c r="R21" t="n">
-        <v>7232809</v>
+        <v>7232589</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,6 +2693,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spillningshög</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2719,32 +2728,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126270183</v>
+        <v>126270129</v>
       </c>
       <c r="B22" t="n">
-        <v>92532</v>
+        <v>57816</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2754,10 +2763,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753979</v>
+        <v>753902</v>
       </c>
       <c r="R22" t="n">
-        <v>7232812</v>
+        <v>7232615</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2820,49 +2829,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126270128</v>
+        <v>126270142</v>
       </c>
       <c r="B23" t="n">
-        <v>56848</v>
+        <v>92724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753884</v>
+        <v>753986</v>
       </c>
       <c r="R23" t="n">
-        <v>7232589</v>
+        <v>7232809</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2895,11 +2900,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spillningshög</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2930,32 +2930,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126270129</v>
+        <v>126270183</v>
       </c>
       <c r="B24" t="n">
-        <v>57816</v>
+        <v>92532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753902</v>
+        <v>753979</v>
       </c>
       <c r="R24" t="n">
-        <v>7232615</v>
+        <v>7232812</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4748,10 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126270130</v>
+        <v>126270169</v>
       </c>
       <c r="B42" t="n">
-        <v>91192</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,21 +4759,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753974</v>
+        <v>754075</v>
       </c>
       <c r="R42" t="n">
-        <v>7232782</v>
+        <v>7232767</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4819,6 +4819,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4849,10 +4854,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126270169</v>
+        <v>126270145</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,21 +4865,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4884,10 +4889,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>754075</v>
+        <v>753910</v>
       </c>
       <c r="R43" t="n">
-        <v>7232767</v>
+        <v>7232666</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4920,11 +4925,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126270145</v>
+        <v>126270157</v>
       </c>
       <c r="B44" t="n">
-        <v>92724</v>
+        <v>78735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753910</v>
+        <v>754037</v>
       </c>
       <c r="R44" t="n">
-        <v>7232666</v>
+        <v>7232824</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5056,10 +5056,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126270157</v>
+        <v>126270167</v>
       </c>
       <c r="B45" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5067,21 +5067,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>754037</v>
+        <v>754064</v>
       </c>
       <c r="R45" t="n">
-        <v>7232824</v>
+        <v>7232752</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126270167</v>
+        <v>126270130</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>91192</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>754064</v>
+        <v>753974</v>
       </c>
       <c r="R46" t="n">
-        <v>7232752</v>
+        <v>7232782</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126270138</v>
+        <v>126270181</v>
       </c>
       <c r="B3" t="n">
-        <v>79001</v>
+        <v>92532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753873</v>
+        <v>754046</v>
       </c>
       <c r="R3" t="n">
-        <v>7232617</v>
+        <v>7232840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126270181</v>
+        <v>126270138</v>
       </c>
       <c r="B4" t="n">
-        <v>92532</v>
+        <v>79001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754046</v>
+        <v>753873</v>
       </c>
       <c r="R4" t="n">
-        <v>7232840</v>
+        <v>7232617</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1188,45 +1188,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126270171</v>
+        <v>126270154</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>57760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754050</v>
+        <v>754057</v>
       </c>
       <c r="R7" t="n">
-        <v>7232814</v>
+        <v>7232729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126270154</v>
+        <v>126270151</v>
       </c>
       <c r="B8" t="n">
         <v>57760</v>
@@ -1332,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754057</v>
+        <v>754019</v>
       </c>
       <c r="R8" t="n">
-        <v>7232729</v>
+        <v>7232699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,53 +1406,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126270151</v>
+        <v>126270171</v>
       </c>
       <c r="B9" t="n">
-        <v>57760</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754019</v>
+        <v>754050</v>
       </c>
       <c r="R9" t="n">
-        <v>7232699</v>
+        <v>7232814</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126270174</v>
+        <v>126270148</v>
       </c>
       <c r="B15" t="n">
-        <v>78644</v>
+        <v>92724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754019</v>
+        <v>753884</v>
       </c>
       <c r="R15" t="n">
-        <v>7232841</v>
+        <v>7232663</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126270148</v>
+        <v>126270174</v>
       </c>
       <c r="B16" t="n">
-        <v>92724</v>
+        <v>78644</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753884</v>
+        <v>754019</v>
       </c>
       <c r="R16" t="n">
-        <v>7232663</v>
+        <v>7232841</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2728,10 +2728,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126270129</v>
+        <v>126270142</v>
       </c>
       <c r="B22" t="n">
-        <v>57816</v>
+        <v>92724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,21 +2739,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753902</v>
+        <v>753986</v>
       </c>
       <c r="R22" t="n">
-        <v>7232615</v>
+        <v>7232809</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,32 +2829,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126270142</v>
+        <v>126270183</v>
       </c>
       <c r="B23" t="n">
-        <v>92724</v>
+        <v>92532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753986</v>
+        <v>753979</v>
       </c>
       <c r="R23" t="n">
-        <v>7232809</v>
+        <v>7232812</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,32 +2930,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126270183</v>
+        <v>126270129</v>
       </c>
       <c r="B24" t="n">
-        <v>92532</v>
+        <v>57816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753979</v>
+        <v>753902</v>
       </c>
       <c r="R24" t="n">
-        <v>7232812</v>
+        <v>7232615</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126270173</v>
+        <v>126270140</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753873</v>
+        <v>754099</v>
       </c>
       <c r="R25" t="n">
-        <v>7232617</v>
+        <v>7232830</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,32 +3132,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126270140</v>
+        <v>126270184</v>
       </c>
       <c r="B26" t="n">
-        <v>92724</v>
+        <v>92532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754099</v>
+        <v>753906</v>
       </c>
       <c r="R26" t="n">
-        <v>7232830</v>
+        <v>7232656</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,32 +3233,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126270137</v>
+        <v>126270139</v>
       </c>
       <c r="B27" t="n">
-        <v>79001</v>
+        <v>92724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6434</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>754063</v>
+        <v>754049</v>
       </c>
       <c r="R27" t="n">
-        <v>7232755</v>
+        <v>7232811</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3334,32 +3334,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126270184</v>
+        <v>126270146</v>
       </c>
       <c r="B28" t="n">
-        <v>92532</v>
+        <v>92724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753906</v>
+        <v>753928</v>
       </c>
       <c r="R28" t="n">
-        <v>7232656</v>
+        <v>7232730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,10 +3435,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126270139</v>
+        <v>126270173</v>
       </c>
       <c r="B29" t="n">
-        <v>92724</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3446,21 +3446,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>754049</v>
+        <v>753873</v>
       </c>
       <c r="R29" t="n">
-        <v>7232811</v>
+        <v>7232617</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,32 +3536,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126270146</v>
+        <v>126270137</v>
       </c>
       <c r="B30" t="n">
-        <v>92724</v>
+        <v>79001</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753928</v>
+        <v>754063</v>
       </c>
       <c r="R30" t="n">
-        <v>7232730</v>
+        <v>7232755</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3839,32 +3839,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126270186</v>
+        <v>126270182</v>
       </c>
       <c r="B33" t="n">
-        <v>77926</v>
+        <v>92532</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>754028</v>
+        <v>753991</v>
       </c>
       <c r="R33" t="n">
-        <v>7232689</v>
+        <v>7232817</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,32 +3940,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126270182</v>
+        <v>126270186</v>
       </c>
       <c r="B34" t="n">
-        <v>92532</v>
+        <v>77926</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753991</v>
+        <v>754028</v>
       </c>
       <c r="R34" t="n">
-        <v>7232817</v>
+        <v>7232689</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4748,10 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126270169</v>
+        <v>126270145</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,21 +4759,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>754075</v>
+        <v>753910</v>
       </c>
       <c r="R42" t="n">
-        <v>7232767</v>
+        <v>7232666</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4819,11 +4819,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4854,10 +4849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126270145</v>
+        <v>126270130</v>
       </c>
       <c r="B43" t="n">
-        <v>92724</v>
+        <v>91192</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,21 +4860,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>112</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4889,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753910</v>
+        <v>753974</v>
       </c>
       <c r="R43" t="n">
-        <v>7232666</v>
+        <v>7232782</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4955,10 +4950,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126270157</v>
+        <v>126270169</v>
       </c>
       <c r="B44" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,21 +4961,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4990,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>754037</v>
+        <v>754075</v>
       </c>
       <c r="R44" t="n">
-        <v>7232824</v>
+        <v>7232767</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5026,6 +5021,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5056,10 +5056,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126270167</v>
+        <v>126270157</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5067,21 +5067,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>754064</v>
+        <v>754037</v>
       </c>
       <c r="R45" t="n">
-        <v>7232752</v>
+        <v>7232824</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126270130</v>
+        <v>126270167</v>
       </c>
       <c r="B46" t="n">
-        <v>91192</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753974</v>
+        <v>754064</v>
       </c>
       <c r="R46" t="n">
-        <v>7232782</v>
+        <v>7232752</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -2618,49 +2618,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126270128</v>
+        <v>126270142</v>
       </c>
       <c r="B21" t="n">
-        <v>56848</v>
+        <v>92724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753884</v>
+        <v>753986</v>
       </c>
       <c r="R21" t="n">
-        <v>7232589</v>
+        <v>7232809</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,11 +2689,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spillningshög</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2728,32 +2719,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126270142</v>
+        <v>126270183</v>
       </c>
       <c r="B22" t="n">
-        <v>92724</v>
+        <v>92532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2763,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753986</v>
+        <v>753979</v>
       </c>
       <c r="R22" t="n">
-        <v>7232809</v>
+        <v>7232812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,10 +2820,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126270183</v>
+        <v>126270128</v>
       </c>
       <c r="B23" t="n">
-        <v>92532</v>
+        <v>56848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,34 +2831,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753979</v>
+        <v>753884</v>
       </c>
       <c r="R23" t="n">
-        <v>7232812</v>
+        <v>7232589</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,6 +2895,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spillningshög</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4849,10 +4849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126270130</v>
+        <v>126270169</v>
       </c>
       <c r="B43" t="n">
-        <v>91192</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753974</v>
+        <v>754075</v>
       </c>
       <c r="R43" t="n">
-        <v>7232782</v>
+        <v>7232767</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4920,6 +4920,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4950,10 +4955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126270169</v>
+        <v>126270157</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4961,21 +4966,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4985,10 +4990,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>754075</v>
+        <v>754037</v>
       </c>
       <c r="R44" t="n">
-        <v>7232767</v>
+        <v>7232824</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5021,11 +5026,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5056,10 +5056,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126270157</v>
+        <v>126270167</v>
       </c>
       <c r="B45" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5067,21 +5067,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>754037</v>
+        <v>754064</v>
       </c>
       <c r="R45" t="n">
-        <v>7232824</v>
+        <v>7232752</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126270167</v>
+        <v>126270130</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>91192</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>754064</v>
+        <v>753974</v>
       </c>
       <c r="R46" t="n">
-        <v>7232752</v>
+        <v>7232782</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126270152</v>
       </c>
       <c r="B2" t="n">
-        <v>57760</v>
+        <v>57761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126270181</v>
+        <v>126270138</v>
       </c>
       <c r="B3" t="n">
-        <v>92532</v>
+        <v>79004</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754046</v>
+        <v>753873</v>
       </c>
       <c r="R3" t="n">
-        <v>7232840</v>
+        <v>7232617</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126270138</v>
+        <v>126270181</v>
       </c>
       <c r="B4" t="n">
-        <v>79001</v>
+        <v>92535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753873</v>
+        <v>754046</v>
       </c>
       <c r="R4" t="n">
-        <v>7232617</v>
+        <v>7232840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
         <v>126270165</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>126270126</v>
       </c>
       <c r="B6" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,53 +1188,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126270154</v>
+        <v>126270171</v>
       </c>
       <c r="B7" t="n">
-        <v>57760</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754057</v>
+        <v>754050</v>
       </c>
       <c r="R7" t="n">
-        <v>7232729</v>
+        <v>7232814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126270151</v>
+        <v>126270154</v>
       </c>
       <c r="B8" t="n">
-        <v>57760</v>
+        <v>57761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754019</v>
+        <v>754057</v>
       </c>
       <c r="R8" t="n">
-        <v>7232699</v>
+        <v>7232729</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,45 +1398,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126270171</v>
+        <v>126270151</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>57761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754050</v>
+        <v>754019</v>
       </c>
       <c r="R9" t="n">
-        <v>7232814</v>
+        <v>7232699</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,7 +1510,7 @@
         <v>126270172</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>126270149</v>
       </c>
       <c r="B11" t="n">
-        <v>80116</v>
+        <v>80119</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>126270141</v>
       </c>
       <c r="B12" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>126270193</v>
       </c>
       <c r="B13" t="n">
-        <v>92526</v>
+        <v>92529</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>126270194</v>
       </c>
       <c r="B14" t="n">
-        <v>92526</v>
+        <v>92529</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>126270148</v>
       </c>
       <c r="B15" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>126270174</v>
       </c>
       <c r="B16" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>126270191</v>
       </c>
       <c r="B17" t="n">
-        <v>92526</v>
+        <v>92529</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>126270196</v>
       </c>
       <c r="B18" t="n">
-        <v>92526</v>
+        <v>92529</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>126270123</v>
       </c>
       <c r="B19" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>126270187</v>
       </c>
       <c r="B20" t="n">
-        <v>77926</v>
+        <v>77929</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>126270142</v>
       </c>
       <c r="B21" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>126270183</v>
       </c>
       <c r="B22" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>126270128</v>
       </c>
       <c r="B23" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>126270129</v>
       </c>
       <c r="B24" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126270140</v>
+        <v>126270173</v>
       </c>
       <c r="B25" t="n">
-        <v>92724</v>
+        <v>78980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754099</v>
+        <v>753873</v>
       </c>
       <c r="R25" t="n">
-        <v>7232830</v>
+        <v>7232617</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126270184</v>
+        <v>126270137</v>
       </c>
       <c r="B26" t="n">
-        <v>92532</v>
+        <v>79004</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3143,21 +3143,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753906</v>
+        <v>754063</v>
       </c>
       <c r="R26" t="n">
-        <v>7232656</v>
+        <v>7232755</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,32 +3233,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126270139</v>
+        <v>126270184</v>
       </c>
       <c r="B27" t="n">
-        <v>92724</v>
+        <v>92535</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>754049</v>
+        <v>753906</v>
       </c>
       <c r="R27" t="n">
-        <v>7232811</v>
+        <v>7232656</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126270146</v>
+        <v>126270140</v>
       </c>
       <c r="B28" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753928</v>
+        <v>754099</v>
       </c>
       <c r="R28" t="n">
-        <v>7232730</v>
+        <v>7232830</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,10 +3435,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126270173</v>
+        <v>126270139</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>92727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3446,21 +3446,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753873</v>
+        <v>754049</v>
       </c>
       <c r="R29" t="n">
-        <v>7232617</v>
+        <v>7232811</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,32 +3536,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126270137</v>
+        <v>126270146</v>
       </c>
       <c r="B30" t="n">
-        <v>79001</v>
+        <v>92727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>754063</v>
+        <v>753928</v>
       </c>
       <c r="R30" t="n">
-        <v>7232755</v>
+        <v>7232730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3640,7 +3640,7 @@
         <v>126270176</v>
       </c>
       <c r="B31" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>126270143</v>
       </c>
       <c r="B32" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3839,32 +3839,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126270182</v>
+        <v>126270186</v>
       </c>
       <c r="B33" t="n">
-        <v>92532</v>
+        <v>77929</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753991</v>
+        <v>754028</v>
       </c>
       <c r="R33" t="n">
-        <v>7232817</v>
+        <v>7232689</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,32 +3940,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126270186</v>
+        <v>126270182</v>
       </c>
       <c r="B34" t="n">
-        <v>77926</v>
+        <v>92535</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>754028</v>
+        <v>753991</v>
       </c>
       <c r="R34" t="n">
-        <v>7232689</v>
+        <v>7232817</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4044,7 +4044,7 @@
         <v>126270124</v>
       </c>
       <c r="B35" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>126270180</v>
       </c>
       <c r="B36" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>126270197</v>
       </c>
       <c r="B37" t="n">
-        <v>78383</v>
+        <v>78386</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>126270122</v>
       </c>
       <c r="B38" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>126270190</v>
       </c>
       <c r="B39" t="n">
-        <v>77926</v>
+        <v>77929</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>126270125</v>
       </c>
       <c r="B40" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>126270170</v>
       </c>
       <c r="B41" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4748,10 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126270145</v>
+        <v>126270169</v>
       </c>
       <c r="B42" t="n">
-        <v>92724</v>
+        <v>78980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,21 +4759,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753910</v>
+        <v>754075</v>
       </c>
       <c r="R42" t="n">
-        <v>7232666</v>
+        <v>7232767</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4819,6 +4819,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4849,10 +4854,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126270169</v>
+        <v>126270157</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,21 +4865,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4884,10 +4889,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>754075</v>
+        <v>754037</v>
       </c>
       <c r="R43" t="n">
-        <v>7232767</v>
+        <v>7232824</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4920,11 +4925,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126270157</v>
+        <v>126270167</v>
       </c>
       <c r="B44" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>754037</v>
+        <v>754064</v>
       </c>
       <c r="R44" t="n">
-        <v>7232824</v>
+        <v>7232752</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5056,10 +5056,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126270167</v>
+        <v>126270130</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>91195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5067,21 +5067,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>754064</v>
+        <v>753974</v>
       </c>
       <c r="R45" t="n">
-        <v>7232752</v>
+        <v>7232782</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126270130</v>
+        <v>126270145</v>
       </c>
       <c r="B46" t="n">
-        <v>91192</v>
+        <v>92727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>112</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753974</v>
+        <v>753910</v>
       </c>
       <c r="R46" t="n">
-        <v>7232782</v>
+        <v>7232666</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5258,10 +5258,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126270175</v>
+        <v>126270144</v>
       </c>
       <c r="B47" t="n">
-        <v>78644</v>
+        <v>92727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5269,21 +5269,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753911</v>
+        <v>753928</v>
       </c>
       <c r="R47" t="n">
-        <v>7232730</v>
+        <v>7232737</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,32 +5359,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126270144</v>
+        <v>126270155</v>
       </c>
       <c r="B48" t="n">
-        <v>92724</v>
+        <v>91173</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>2013</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5394,10 +5394,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753928</v>
+        <v>753884</v>
       </c>
       <c r="R48" t="n">
-        <v>7232737</v>
+        <v>7232663</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5438,6 +5438,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5460,32 +5461,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126270155</v>
+        <v>126270175</v>
       </c>
       <c r="B49" t="n">
-        <v>91170</v>
+        <v>78647</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2013</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5495,10 +5496,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753884</v>
+        <v>753911</v>
       </c>
       <c r="R49" t="n">
-        <v>7232663</v>
+        <v>7232730</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5539,7 +5540,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5565,7 +5565,7 @@
         <v>126270127</v>
       </c>
       <c r="B50" t="n">
-        <v>91527</v>
+        <v>91530</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -2719,10 +2719,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126270183</v>
+        <v>126270128</v>
       </c>
       <c r="B22" t="n">
-        <v>92535</v>
+        <v>56849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,34 +2730,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753979</v>
+        <v>753884</v>
       </c>
       <c r="R22" t="n">
-        <v>7232812</v>
+        <v>7232589</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,6 +2794,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillningshög</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2820,10 +2829,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126270128</v>
+        <v>126270183</v>
       </c>
       <c r="B23" t="n">
-        <v>56849</v>
+        <v>92535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2831,38 +2840,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753884</v>
+        <v>753979</v>
       </c>
       <c r="R23" t="n">
-        <v>7232589</v>
+        <v>7232812</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2895,11 +2900,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spillningshög</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -784,32 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126270138</v>
+        <v>126270165</v>
       </c>
       <c r="B3" t="n">
-        <v>79004</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753873</v>
+        <v>754052</v>
       </c>
       <c r="R3" t="n">
-        <v>7232617</v>
+        <v>7232732</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,32 +885,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126270181</v>
+        <v>126270126</v>
       </c>
       <c r="B4" t="n">
-        <v>92535</v>
+        <v>79598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754046</v>
+        <v>754089</v>
       </c>
       <c r="R4" t="n">
-        <v>7232840</v>
+        <v>7232834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126270165</v>
+        <v>126270138</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754052</v>
+        <v>753873</v>
       </c>
       <c r="R5" t="n">
-        <v>7232732</v>
+        <v>7232617</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,32 +1087,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126270126</v>
+        <v>126270181</v>
       </c>
       <c r="B6" t="n">
-        <v>79598</v>
+        <v>92535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>754089</v>
+        <v>754046</v>
       </c>
       <c r="R6" t="n">
-        <v>7232834</v>
+        <v>7232840</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126270148</v>
+        <v>126270174</v>
       </c>
       <c r="B15" t="n">
-        <v>92727</v>
+        <v>78647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753884</v>
+        <v>754019</v>
       </c>
       <c r="R15" t="n">
-        <v>7232663</v>
+        <v>7232841</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126270174</v>
+        <v>126270148</v>
       </c>
       <c r="B16" t="n">
-        <v>78647</v>
+        <v>92727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754019</v>
+        <v>753884</v>
       </c>
       <c r="R16" t="n">
-        <v>7232841</v>
+        <v>7232663</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2719,10 +2719,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126270128</v>
+        <v>126270183</v>
       </c>
       <c r="B22" t="n">
-        <v>56849</v>
+        <v>92535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,38 +2730,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753884</v>
+        <v>753979</v>
       </c>
       <c r="R22" t="n">
-        <v>7232589</v>
+        <v>7232812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2794,11 +2790,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillningshög</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2829,10 +2820,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126270183</v>
+        <v>126270128</v>
       </c>
       <c r="B23" t="n">
-        <v>92535</v>
+        <v>56849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,34 +2831,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753979</v>
+        <v>753884</v>
       </c>
       <c r="R23" t="n">
-        <v>7232812</v>
+        <v>7232589</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,6 +2895,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spillningshög</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126270173</v>
+        <v>126270140</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>92727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753873</v>
+        <v>754099</v>
       </c>
       <c r="R25" t="n">
-        <v>7232617</v>
+        <v>7232830</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,32 +3132,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126270137</v>
+        <v>126270139</v>
       </c>
       <c r="B26" t="n">
-        <v>79004</v>
+        <v>92727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6434</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754063</v>
+        <v>754049</v>
       </c>
       <c r="R26" t="n">
-        <v>7232755</v>
+        <v>7232811</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,32 +3233,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126270184</v>
+        <v>126270146</v>
       </c>
       <c r="B27" t="n">
-        <v>92535</v>
+        <v>92727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753906</v>
+        <v>753928</v>
       </c>
       <c r="R27" t="n">
-        <v>7232656</v>
+        <v>7232730</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3334,32 +3334,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126270140</v>
+        <v>126270184</v>
       </c>
       <c r="B28" t="n">
-        <v>92727</v>
+        <v>92535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>754099</v>
+        <v>753906</v>
       </c>
       <c r="R28" t="n">
-        <v>7232830</v>
+        <v>7232656</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,10 +3435,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126270139</v>
+        <v>126270173</v>
       </c>
       <c r="B29" t="n">
-        <v>92727</v>
+        <v>78980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3446,21 +3446,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>754049</v>
+        <v>753873</v>
       </c>
       <c r="R29" t="n">
-        <v>7232811</v>
+        <v>7232617</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,32 +3536,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126270146</v>
+        <v>126270137</v>
       </c>
       <c r="B30" t="n">
-        <v>92727</v>
+        <v>79004</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753928</v>
+        <v>754063</v>
       </c>
       <c r="R30" t="n">
-        <v>7232730</v>
+        <v>7232755</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126270176</v>
+        <v>126270186</v>
       </c>
       <c r="B31" t="n">
-        <v>78647</v>
+        <v>77929</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3648,21 +3648,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753946</v>
+        <v>754028</v>
       </c>
       <c r="R31" t="n">
-        <v>7232791</v>
+        <v>7232689</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3738,10 +3738,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126270143</v>
+        <v>126270176</v>
       </c>
       <c r="B32" t="n">
-        <v>92727</v>
+        <v>78647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3749,21 +3749,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753997</v>
+        <v>753946</v>
       </c>
       <c r="R32" t="n">
-        <v>7232748</v>
+        <v>7232791</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126270186</v>
+        <v>126270143</v>
       </c>
       <c r="B33" t="n">
-        <v>77929</v>
+        <v>92727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>754028</v>
+        <v>753997</v>
       </c>
       <c r="R33" t="n">
-        <v>7232689</v>
+        <v>7232748</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4243,32 +4243,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126270197</v>
+        <v>126270122</v>
       </c>
       <c r="B37" t="n">
-        <v>78386</v>
+        <v>91210</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>754065</v>
+        <v>754070</v>
       </c>
       <c r="R37" t="n">
-        <v>7232758</v>
+        <v>7232862</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4344,32 +4344,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126270122</v>
+        <v>126270197</v>
       </c>
       <c r="B38" t="n">
-        <v>91210</v>
+        <v>78386</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>754070</v>
+        <v>754065</v>
       </c>
       <c r="R38" t="n">
-        <v>7232862</v>
+        <v>7232758</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4748,10 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126270169</v>
+        <v>126270157</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,21 +4759,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>754075</v>
+        <v>754037</v>
       </c>
       <c r="R42" t="n">
-        <v>7232767</v>
+        <v>7232824</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4819,11 +4819,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4854,10 +4849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126270157</v>
+        <v>126270169</v>
       </c>
       <c r="B43" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,21 +4860,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4889,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>754037</v>
+        <v>754075</v>
       </c>
       <c r="R43" t="n">
-        <v>7232824</v>
+        <v>7232767</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4925,6 +4920,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5056,10 +5056,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126270130</v>
+        <v>126270145</v>
       </c>
       <c r="B45" t="n">
-        <v>91195</v>
+        <v>92727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5067,21 +5067,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>112</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753974</v>
+        <v>753910</v>
       </c>
       <c r="R45" t="n">
-        <v>7232782</v>
+        <v>7232666</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126270145</v>
+        <v>126270130</v>
       </c>
       <c r="B46" t="n">
-        <v>92727</v>
+        <v>91195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>112</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753910</v>
+        <v>753974</v>
       </c>
       <c r="R46" t="n">
-        <v>7232666</v>
+        <v>7232782</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5258,10 +5258,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126270144</v>
+        <v>126270175</v>
       </c>
       <c r="B47" t="n">
-        <v>92727</v>
+        <v>78647</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5269,21 +5269,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753928</v>
+        <v>753911</v>
       </c>
       <c r="R47" t="n">
-        <v>7232737</v>
+        <v>7232730</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,32 +5359,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126270155</v>
+        <v>126270144</v>
       </c>
       <c r="B48" t="n">
-        <v>91173</v>
+        <v>92727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2013</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5394,10 +5394,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753884</v>
+        <v>753928</v>
       </c>
       <c r="R48" t="n">
-        <v>7232663</v>
+        <v>7232737</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5438,7 +5438,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5461,32 +5460,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126270175</v>
+        <v>126270155</v>
       </c>
       <c r="B49" t="n">
-        <v>78647</v>
+        <v>91173</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>2013</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5496,10 +5495,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753911</v>
+        <v>753884</v>
       </c>
       <c r="R49" t="n">
-        <v>7232730</v>
+        <v>7232663</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5540,6 +5539,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -1188,45 +1188,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126270171</v>
+        <v>126270154</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>57761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754050</v>
+        <v>754057</v>
       </c>
       <c r="R7" t="n">
-        <v>7232814</v>
+        <v>7232729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126270154</v>
+        <v>126270151</v>
       </c>
       <c r="B8" t="n">
         <v>57761</v>
@@ -1332,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754057</v>
+        <v>754019</v>
       </c>
       <c r="R8" t="n">
-        <v>7232729</v>
+        <v>7232699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,53 +1406,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126270151</v>
+        <v>126270171</v>
       </c>
       <c r="B9" t="n">
-        <v>57761</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754019</v>
+        <v>754050</v>
       </c>
       <c r="R9" t="n">
-        <v>7232699</v>
+        <v>7232814</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126270174</v>
+        <v>126270148</v>
       </c>
       <c r="B15" t="n">
-        <v>78647</v>
+        <v>92727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754019</v>
+        <v>753884</v>
       </c>
       <c r="R15" t="n">
-        <v>7232841</v>
+        <v>7232663</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126270148</v>
+        <v>126270174</v>
       </c>
       <c r="B16" t="n">
-        <v>92727</v>
+        <v>78647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753884</v>
+        <v>754019</v>
       </c>
       <c r="R16" t="n">
-        <v>7232663</v>
+        <v>7232841</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126270142</v>
+        <v>126270129</v>
       </c>
       <c r="B21" t="n">
-        <v>92727</v>
+        <v>57817</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753986</v>
+        <v>753902</v>
       </c>
       <c r="R21" t="n">
-        <v>7232809</v>
+        <v>7232615</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126270129</v>
+        <v>126270142</v>
       </c>
       <c r="B24" t="n">
-        <v>57817</v>
+        <v>92727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2941,21 +2941,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753902</v>
+        <v>753986</v>
       </c>
       <c r="R24" t="n">
-        <v>7232615</v>
+        <v>7232809</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126270186</v>
+        <v>126270176</v>
       </c>
       <c r="B31" t="n">
-        <v>77929</v>
+        <v>78647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3648,21 +3648,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>754028</v>
+        <v>753946</v>
       </c>
       <c r="R31" t="n">
-        <v>7232689</v>
+        <v>7232791</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3738,10 +3738,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126270176</v>
+        <v>126270143</v>
       </c>
       <c r="B32" t="n">
-        <v>78647</v>
+        <v>92727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3749,21 +3749,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753946</v>
+        <v>753997</v>
       </c>
       <c r="R32" t="n">
-        <v>7232791</v>
+        <v>7232748</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,32 +3839,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126270143</v>
+        <v>126270182</v>
       </c>
       <c r="B33" t="n">
-        <v>92727</v>
+        <v>92535</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753997</v>
+        <v>753991</v>
       </c>
       <c r="R33" t="n">
-        <v>7232748</v>
+        <v>7232817</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,32 +3940,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126270182</v>
+        <v>126270186</v>
       </c>
       <c r="B34" t="n">
-        <v>92535</v>
+        <v>77929</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753991</v>
+        <v>754028</v>
       </c>
       <c r="R34" t="n">
-        <v>7232817</v>
+        <v>7232689</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4748,10 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126270157</v>
+        <v>126270145</v>
       </c>
       <c r="B42" t="n">
-        <v>78738</v>
+        <v>92727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,21 +4759,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>754037</v>
+        <v>753910</v>
       </c>
       <c r="R42" t="n">
-        <v>7232824</v>
+        <v>7232666</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4849,10 +4849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126270169</v>
+        <v>126270130</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>91195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>754075</v>
+        <v>753974</v>
       </c>
       <c r="R43" t="n">
-        <v>7232767</v>
+        <v>7232782</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4920,11 +4920,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4955,10 +4950,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126270167</v>
+        <v>126270157</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,21 +4961,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4990,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>754064</v>
+        <v>754037</v>
       </c>
       <c r="R44" t="n">
-        <v>7232752</v>
+        <v>7232824</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5056,10 +5051,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126270145</v>
+        <v>126270169</v>
       </c>
       <c r="B45" t="n">
-        <v>92727</v>
+        <v>78980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5067,21 +5062,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5091,10 +5086,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753910</v>
+        <v>754075</v>
       </c>
       <c r="R45" t="n">
-        <v>7232666</v>
+        <v>7232767</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5127,6 +5122,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5157,10 +5157,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126270130</v>
+        <v>126270167</v>
       </c>
       <c r="B46" t="n">
-        <v>91195</v>
+        <v>78980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753974</v>
+        <v>754064</v>
       </c>
       <c r="R46" t="n">
-        <v>7232782</v>
+        <v>7232752</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -1188,53 +1188,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126270154</v>
+        <v>126270171</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754057</v>
+        <v>754050</v>
       </c>
       <c r="R7" t="n">
-        <v>7232729</v>
+        <v>7232814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1289,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126270151</v>
+        <v>126270154</v>
       </c>
       <c r="B8" t="n">
         <v>57761</v>
@@ -1340,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754019</v>
+        <v>754057</v>
       </c>
       <c r="R8" t="n">
-        <v>7232699</v>
+        <v>7232729</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,45 +1398,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126270171</v>
+        <v>126270151</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>57761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754050</v>
+        <v>754019</v>
       </c>
       <c r="R9" t="n">
-        <v>7232814</v>
+        <v>7232699</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -4041,32 +4041,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126270124</v>
+        <v>126270180</v>
       </c>
       <c r="B35" t="n">
-        <v>79598</v>
+        <v>92535</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>754057</v>
+        <v>754036</v>
       </c>
       <c r="R35" t="n">
-        <v>7232734</v>
+        <v>7232745</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4142,32 +4142,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126270180</v>
+        <v>126270124</v>
       </c>
       <c r="B36" t="n">
-        <v>92535</v>
+        <v>79598</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>754036</v>
+        <v>754057</v>
       </c>
       <c r="R36" t="n">
-        <v>7232745</v>
+        <v>7232734</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126270148</v>
+        <v>126270174</v>
       </c>
       <c r="B15" t="n">
-        <v>92727</v>
+        <v>78647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753884</v>
+        <v>754019</v>
       </c>
       <c r="R15" t="n">
-        <v>7232663</v>
+        <v>7232841</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126270174</v>
+        <v>126270148</v>
       </c>
       <c r="B16" t="n">
-        <v>78647</v>
+        <v>92727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754019</v>
+        <v>753884</v>
       </c>
       <c r="R16" t="n">
-        <v>7232841</v>
+        <v>7232663</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126270129</v>
+        <v>126270142</v>
       </c>
       <c r="B21" t="n">
-        <v>57817</v>
+        <v>92727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753902</v>
+        <v>753986</v>
       </c>
       <c r="R21" t="n">
-        <v>7232615</v>
+        <v>7232809</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126270142</v>
+        <v>126270129</v>
       </c>
       <c r="B24" t="n">
-        <v>92727</v>
+        <v>57817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2941,21 +2941,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753986</v>
+        <v>753902</v>
       </c>
       <c r="R24" t="n">
-        <v>7232809</v>
+        <v>7232615</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126270176</v>
+        <v>126270186</v>
       </c>
       <c r="B31" t="n">
-        <v>78647</v>
+        <v>77929</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3648,21 +3648,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753946</v>
+        <v>754028</v>
       </c>
       <c r="R31" t="n">
-        <v>7232791</v>
+        <v>7232689</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3738,10 +3738,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126270143</v>
+        <v>126270176</v>
       </c>
       <c r="B32" t="n">
-        <v>92727</v>
+        <v>78647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3749,21 +3749,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753997</v>
+        <v>753946</v>
       </c>
       <c r="R32" t="n">
-        <v>7232748</v>
+        <v>7232791</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,32 +3839,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126270182</v>
+        <v>126270143</v>
       </c>
       <c r="B33" t="n">
-        <v>92535</v>
+        <v>92727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753991</v>
+        <v>753997</v>
       </c>
       <c r="R33" t="n">
-        <v>7232817</v>
+        <v>7232748</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,32 +3940,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126270186</v>
+        <v>126270182</v>
       </c>
       <c r="B34" t="n">
-        <v>77929</v>
+        <v>92535</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>754028</v>
+        <v>753991</v>
       </c>
       <c r="R34" t="n">
-        <v>7232689</v>
+        <v>7232817</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,32 +4041,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126270180</v>
+        <v>126270124</v>
       </c>
       <c r="B35" t="n">
-        <v>92535</v>
+        <v>79598</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>754036</v>
+        <v>754057</v>
       </c>
       <c r="R35" t="n">
-        <v>7232745</v>
+        <v>7232734</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4142,32 +4142,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126270124</v>
+        <v>126270180</v>
       </c>
       <c r="B36" t="n">
-        <v>79598</v>
+        <v>92535</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>754057</v>
+        <v>754036</v>
       </c>
       <c r="R36" t="n">
-        <v>7232734</v>
+        <v>7232745</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -5537,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="AE49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126270152</v>
+        <v>126270127</v>
       </c>
       <c r="B2" t="n">
-        <v>57761</v>
+        <v>92198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>71</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754023</v>
+        <v>753997</v>
       </c>
       <c r="R2" t="n">
-        <v>7232724</v>
+        <v>7232748</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,12 +751,18 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Blev lätt till pulver när den rullades mellan fingrarna. Växte på den ännu stenhårda kärnveden inuti lågan, satt fast rätt ordentligt i underlaget. Tjock och "bullig", med porer hela vägen till kanten</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126270165</v>
+        <v>126270130</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754052</v>
+        <v>753974</v>
       </c>
       <c r="R3" t="n">
-        <v>7232732</v>
+        <v>7232782</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126270126</v>
+        <v>126270174</v>
       </c>
       <c r="B4" t="n">
-        <v>79598</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +897,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754089</v>
+        <v>754019</v>
       </c>
       <c r="R4" t="n">
-        <v>7232834</v>
+        <v>7232841</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,32 +987,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126270138</v>
+        <v>126270175</v>
       </c>
       <c r="B5" t="n">
-        <v>79004</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753873</v>
+        <v>753911</v>
       </c>
       <c r="R5" t="n">
-        <v>7232617</v>
+        <v>7232730</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,32 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126270181</v>
+        <v>126270176</v>
       </c>
       <c r="B6" t="n">
-        <v>92535</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>754046</v>
+        <v>753946</v>
       </c>
       <c r="R6" t="n">
-        <v>7232840</v>
+        <v>7232791</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,53 +1189,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126270154</v>
+        <v>126270155</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>91837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>2013</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754057</v>
+        <v>753884</v>
       </c>
       <c r="R7" t="n">
-        <v>7232729</v>
+        <v>7232663</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,8 +1266,9 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1297,53 +1291,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126270151</v>
+        <v>126270139</v>
       </c>
       <c r="B8" t="n">
-        <v>57761</v>
+        <v>91962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754019</v>
+        <v>754049</v>
       </c>
       <c r="R8" t="n">
-        <v>7232699</v>
+        <v>7232811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126270171</v>
+        <v>126270140</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>91962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1417,21 +1403,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1441,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754050</v>
+        <v>754099</v>
       </c>
       <c r="R9" t="n">
-        <v>7232814</v>
+        <v>7232830</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,10 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126270172</v>
+        <v>126270141</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>91962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,21 +1504,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>754070</v>
+        <v>754012</v>
       </c>
       <c r="R10" t="n">
-        <v>7232862</v>
+        <v>7232803</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,32 +1594,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126270149</v>
+        <v>126270142</v>
       </c>
       <c r="B11" t="n">
-        <v>80119</v>
+        <v>91962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753849</v>
+        <v>753986</v>
       </c>
       <c r="R11" t="n">
-        <v>7232635</v>
+        <v>7232809</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126270141</v>
+        <v>126270143</v>
       </c>
       <c r="B12" t="n">
-        <v>92727</v>
+        <v>91962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1744,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>754012</v>
+        <v>753997</v>
       </c>
       <c r="R12" t="n">
-        <v>7232803</v>
+        <v>7232748</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,10 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126270193</v>
+        <v>126270144</v>
       </c>
       <c r="B13" t="n">
-        <v>92529</v>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1821,21 +1807,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1845,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753942</v>
+        <v>753928</v>
       </c>
       <c r="R13" t="n">
-        <v>7232732</v>
+        <v>7232737</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126270194</v>
+        <v>126270145</v>
       </c>
       <c r="B14" t="n">
-        <v>92529</v>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1922,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1946,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753921</v>
+        <v>753910</v>
       </c>
       <c r="R14" t="n">
-        <v>7232723</v>
+        <v>7232666</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126270174</v>
+        <v>126270146</v>
       </c>
       <c r="B15" t="n">
-        <v>78647</v>
+        <v>91962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2047,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754019</v>
+        <v>753928</v>
       </c>
       <c r="R15" t="n">
-        <v>7232841</v>
+        <v>7232730</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,7 +2102,7 @@
         <v>126270148</v>
       </c>
       <c r="B16" t="n">
-        <v>92727</v>
+        <v>91962</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2203,7 @@
         <v>126270191</v>
       </c>
       <c r="B17" t="n">
-        <v>92529</v>
+        <v>93191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126270196</v>
+        <v>126270193</v>
       </c>
       <c r="B18" t="n">
-        <v>92529</v>
+        <v>93191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2350,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753979</v>
+        <v>753942</v>
       </c>
       <c r="R18" t="n">
-        <v>7232812</v>
+        <v>7232732</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2416,32 +2402,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126270123</v>
+        <v>126270194</v>
       </c>
       <c r="B19" t="n">
-        <v>91210</v>
+        <v>93191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2451,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753949</v>
+        <v>753921</v>
       </c>
       <c r="R19" t="n">
-        <v>7232720</v>
+        <v>7232723</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2517,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126270187</v>
+        <v>126270196</v>
       </c>
       <c r="B20" t="n">
-        <v>77929</v>
+        <v>93191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2528,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2552,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754065</v>
+        <v>753979</v>
       </c>
       <c r="R20" t="n">
-        <v>7232758</v>
+        <v>7232812</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2604,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126270129</v>
+        <v>125830900</v>
       </c>
       <c r="B21" t="n">
-        <v>57817</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2615,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2639,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753902</v>
+        <v>754156</v>
       </c>
       <c r="R21" t="n">
-        <v>7232615</v>
+        <v>7232842</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,12 +2669,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2719,14 +2705,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126270183</v>
+        <v>126270180</v>
       </c>
       <c r="B22" t="n">
-        <v>92535</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2754,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753979</v>
+        <v>754036</v>
       </c>
       <c r="R22" t="n">
-        <v>7232812</v>
+        <v>7232745</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2820,49 +2806,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126270128</v>
+        <v>126270181</v>
       </c>
       <c r="B23" t="n">
-        <v>56849</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753884</v>
+        <v>754046</v>
       </c>
       <c r="R23" t="n">
-        <v>7232589</v>
+        <v>7232840</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2895,11 +2877,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spillningshög</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2930,10 +2907,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126270142</v>
+        <v>126270182</v>
       </c>
       <c r="B24" t="n">
-        <v>92727</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2941,21 +2918,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2965,10 +2942,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753986</v>
+        <v>753991</v>
       </c>
       <c r="R24" t="n">
-        <v>7232809</v>
+        <v>7232817</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3008,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126270140</v>
+        <v>126270183</v>
       </c>
       <c r="B25" t="n">
-        <v>92727</v>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,21 +3019,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3043,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754099</v>
+        <v>753979</v>
       </c>
       <c r="R25" t="n">
-        <v>7232830</v>
+        <v>7232812</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,10 +3109,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126270139</v>
+        <v>126270184</v>
       </c>
       <c r="B26" t="n">
-        <v>92727</v>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3143,21 +3120,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3167,10 +3144,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754049</v>
+        <v>753906</v>
       </c>
       <c r="R26" t="n">
-        <v>7232811</v>
+        <v>7232656</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,32 +3210,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126270146</v>
+        <v>126270122</v>
       </c>
       <c r="B27" t="n">
-        <v>92727</v>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3268,10 +3245,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753928</v>
+        <v>754070</v>
       </c>
       <c r="R27" t="n">
-        <v>7232730</v>
+        <v>7232862</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3334,10 +3311,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126270184</v>
+        <v>126270123</v>
       </c>
       <c r="B28" t="n">
-        <v>92535</v>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3345,21 +3322,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3369,10 +3346,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753906</v>
+        <v>753949</v>
       </c>
       <c r="R28" t="n">
-        <v>7232656</v>
+        <v>7232720</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,14 +3412,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126270173</v>
+        <v>125830887</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3470,10 +3447,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753873</v>
+        <v>754137</v>
       </c>
       <c r="R29" t="n">
-        <v>7232617</v>
+        <v>7232854</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3500,12 +3477,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3536,32 +3513,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126270137</v>
+        <v>126270165</v>
       </c>
       <c r="B30" t="n">
-        <v>79004</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>754063</v>
+        <v>754052</v>
       </c>
       <c r="R30" t="n">
-        <v>7232755</v>
+        <v>7232732</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3637,32 +3614,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126270176</v>
+        <v>126270167</v>
       </c>
       <c r="B31" t="n">
-        <v>78647</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3672,10 +3649,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753946</v>
+        <v>754064</v>
       </c>
       <c r="R31" t="n">
-        <v>7232791</v>
+        <v>7232752</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3738,32 +3715,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126270143</v>
+        <v>126270169</v>
       </c>
       <c r="B32" t="n">
-        <v>92727</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3773,10 +3750,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753997</v>
+        <v>754075</v>
       </c>
       <c r="R32" t="n">
-        <v>7232748</v>
+        <v>7232767</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,6 +3786,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3839,32 +3821,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126270182</v>
+        <v>126270170</v>
       </c>
       <c r="B33" t="n">
-        <v>92535</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3874,10 +3856,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753991</v>
+        <v>754078</v>
       </c>
       <c r="R33" t="n">
-        <v>7232817</v>
+        <v>7232778</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,32 +3922,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126270186</v>
+        <v>126270171</v>
       </c>
       <c r="B34" t="n">
-        <v>77929</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3975,10 +3957,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>754028</v>
+        <v>754050</v>
       </c>
       <c r="R34" t="n">
-        <v>7232689</v>
+        <v>7232814</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,32 +4023,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126270124</v>
+        <v>126270172</v>
       </c>
       <c r="B35" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4076,10 +4058,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>754057</v>
+        <v>754070</v>
       </c>
       <c r="R35" t="n">
-        <v>7232734</v>
+        <v>7232862</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4142,32 +4124,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126270180</v>
+        <v>126270173</v>
       </c>
       <c r="B36" t="n">
-        <v>92535</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4177,10 +4159,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>754036</v>
+        <v>753873</v>
       </c>
       <c r="R36" t="n">
-        <v>7232745</v>
+        <v>7232617</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,10 +4225,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126270122</v>
+        <v>126270137</v>
       </c>
       <c r="B37" t="n">
-        <v>91210</v>
+        <v>79351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4254,21 +4236,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4278,10 +4260,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>754070</v>
+        <v>754063</v>
       </c>
       <c r="R37" t="n">
-        <v>7232862</v>
+        <v>7232755</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4344,32 +4326,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126270197</v>
+        <v>126270138</v>
       </c>
       <c r="B38" t="n">
-        <v>78386</v>
+        <v>79351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4379,10 +4361,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>754065</v>
+        <v>753873</v>
       </c>
       <c r="R38" t="n">
-        <v>7232758</v>
+        <v>7232617</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4445,10 +4427,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126270190</v>
+        <v>126270197</v>
       </c>
       <c r="B39" t="n">
-        <v>77929</v>
+        <v>78730</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4456,21 +4438,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4480,10 +4462,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>754038</v>
+        <v>754065</v>
       </c>
       <c r="R39" t="n">
-        <v>7232823</v>
+        <v>7232758</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4546,10 +4528,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126270125</v>
+        <v>126270157</v>
       </c>
       <c r="B40" t="n">
-        <v>79598</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4557,21 +4539,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4581,10 +4563,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>754064</v>
+        <v>754037</v>
       </c>
       <c r="R40" t="n">
-        <v>7232750</v>
+        <v>7232824</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4647,10 +4629,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126270170</v>
+        <v>126270124</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,21 +4640,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,10 +4664,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>754078</v>
+        <v>754057</v>
       </c>
       <c r="R41" t="n">
-        <v>7232778</v>
+        <v>7232734</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4748,10 +4730,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126270145</v>
+        <v>126270125</v>
       </c>
       <c r="B42" t="n">
-        <v>92727</v>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,21 +4741,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4765,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753910</v>
+        <v>754064</v>
       </c>
       <c r="R42" t="n">
-        <v>7232666</v>
+        <v>7232750</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4849,10 +4831,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126270130</v>
+        <v>126270126</v>
       </c>
       <c r="B43" t="n">
-        <v>91195</v>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,21 +4842,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>112</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4884,10 +4866,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753974</v>
+        <v>754089</v>
       </c>
       <c r="R43" t="n">
-        <v>7232782</v>
+        <v>7232834</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4950,32 +4932,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126270157</v>
+        <v>126270149</v>
       </c>
       <c r="B44" t="n">
-        <v>78738</v>
+        <v>80468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4985,10 +4967,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>754037</v>
+        <v>753849</v>
       </c>
       <c r="R44" t="n">
-        <v>7232824</v>
+        <v>7232635</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5051,10 +5033,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126270169</v>
+        <v>126270186</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>78334</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5062,21 +5044,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5086,10 +5068,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>754075</v>
+        <v>754028</v>
       </c>
       <c r="R45" t="n">
-        <v>7232767</v>
+        <v>7232689</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5122,11 +5104,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5157,10 +5134,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126270167</v>
+        <v>126270187</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>78334</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5168,21 +5145,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5192,10 +5169,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>754064</v>
+        <v>754065</v>
       </c>
       <c r="R46" t="n">
-        <v>7232752</v>
+        <v>7232758</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5258,10 +5235,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126270175</v>
+        <v>126270190</v>
       </c>
       <c r="B47" t="n">
-        <v>78647</v>
+        <v>78334</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5269,21 +5246,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5293,10 +5270,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753911</v>
+        <v>754038</v>
       </c>
       <c r="R47" t="n">
-        <v>7232730</v>
+        <v>7232823</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,45 +5336,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126270144</v>
+        <v>126270128</v>
       </c>
       <c r="B48" t="n">
-        <v>92727</v>
+        <v>57141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753928</v>
+        <v>753884</v>
       </c>
       <c r="R48" t="n">
-        <v>7232737</v>
+        <v>7232589</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5430,6 +5411,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spillningshög</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5460,32 +5446,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126270155</v>
+        <v>125830876</v>
       </c>
       <c r="B49" t="n">
-        <v>91173</v>
+        <v>58114</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2013</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5495,10 +5481,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753884</v>
+        <v>754171</v>
       </c>
       <c r="R49" t="n">
-        <v>7232663</v>
+        <v>7232818</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5525,21 +5511,20 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF49" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5562,48 +5547,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126270127</v>
+        <v>126270129</v>
       </c>
       <c r="B50" t="n">
-        <v>91530</v>
+        <v>58114</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>71</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753997</v>
+        <v>753902</v>
       </c>
       <c r="R50" t="n">
-        <v>7232748</v>
+        <v>7232615</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5638,18 +5620,12 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Blev lätt till pulver när den rullades mellan fingrarna. Växte på den ännu stenhårda kärnveden inuti lågan, satt fast rätt ordentligt i underlaget. Tjock och "bullig", med porer hela vägen till kanten</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5665,6 +5641,435 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126270151</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Snörsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>754019</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7232699</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126270152</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Snörsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>754023</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7232724</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126270154</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Snörsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>754057</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7232729</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125830873</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Snörsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>754163</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7232822</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5648,10 +5648,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126270151</v>
+        <v>135183830</v>
       </c>
       <c r="B51" t="n">
-        <v>58057</v>
+        <v>58136</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5659,31 +5659,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5691,10 +5687,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>754019</v>
+        <v>753920</v>
       </c>
       <c r="R51" t="n">
-        <v>7232699</v>
+        <v>7232665</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5721,12 +5717,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Flera stycken i grupp, läten osv även synobs</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5749,18 +5760,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126270152</v>
+        <v>135183831</v>
       </c>
       <c r="B52" t="n">
-        <v>58057</v>
+        <v>58136</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5768,21 +5775,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5790,7 +5797,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5800,10 +5807,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>754023</v>
+        <v>753929</v>
       </c>
       <c r="R52" t="n">
-        <v>7232724</v>
+        <v>7232725</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5830,12 +5837,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5858,18 +5880,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126270154</v>
+        <v>135183832</v>
       </c>
       <c r="B53" t="n">
-        <v>58057</v>
+        <v>58136</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5877,21 +5895,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5899,7 +5917,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5909,10 +5927,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>754057</v>
+        <v>754077</v>
       </c>
       <c r="R53" t="n">
-        <v>7232729</v>
+        <v>7232835</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5939,12 +5957,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5967,18 +6000,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125830873</v>
+        <v>126270151</v>
       </c>
       <c r="B54" t="n">
-        <v>79917</v>
+        <v>58057</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5986,34 +6015,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>754163</v>
+        <v>754019</v>
       </c>
       <c r="R54" t="n">
-        <v>7232822</v>
+        <v>7232699</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6040,12 +6077,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6054,7 +6091,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6070,6 +6106,326 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126270152</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Snörsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>754023</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7232724</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126270154</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Snörsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>754057</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7232729</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125830873</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Snörsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>754163</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7232822</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270127</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270130</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270174</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270175</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270176</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270155</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270139</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270140</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1591,6 +1636,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270141</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270142</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270143</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1894,6 +1954,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270144</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1995,6 +2060,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270145</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2096,6 +2166,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270146</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270148</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2298,6 +2378,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270191</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2399,6 +2484,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270193</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2500,6 +2590,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270194</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2601,6 +2696,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270196</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2702,6 +2802,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125830900</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,6 +2908,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270180</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2904,6 +3014,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270181</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3005,6 +3120,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270182</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3106,6 +3226,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270183</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3207,6 +3332,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270184</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3308,6 +3438,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270122</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3409,6 +3544,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270123</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3510,6 +3650,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125830887</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3611,6 +3756,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270165</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3712,6 +3862,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270167</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3818,6 +3973,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270169</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3919,6 +4079,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270170</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4020,6 +4185,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270171</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4121,6 +4291,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270172</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4222,6 +4397,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270173</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4323,6 +4503,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270137</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4424,6 +4609,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270138</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4525,6 +4715,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270197</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4626,6 +4821,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270157</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4727,6 +4927,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270124</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4828,6 +5033,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270125</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4929,6 +5139,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270126</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5030,6 +5245,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270149</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5131,6 +5351,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270186</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5232,6 +5457,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270187</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5331,6 +5561,11 @@
       <c r="AY47" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270190</t>
         </is>
       </c>
     </row>
@@ -5443,6 +5678,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270128</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5544,6 +5784,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125830876</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5643,6 +5888,11 @@
       <c r="AY50" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270129</t>
         </is>
       </c>
     </row>
@@ -5761,6 +6011,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183830</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5881,6 +6136,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183831</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6001,6 +6261,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183832</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6110,6 +6375,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270151</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6219,6 +6489,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270152</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6328,6 +6603,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270154</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6430,8 +6710,71 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125830873</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -5901,7 +5901,7 @@
         <v>135183830</v>
       </c>
       <c r="B51" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>135183831</v>
       </c>
       <c r="B52" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>135183832</v>
       </c>
       <c r="B53" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ54"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5898,10 +5898,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126270151</v>
+        <v>135183830</v>
       </c>
       <c r="B51" t="n">
-        <v>58057</v>
+        <v>58141</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5909,31 +5909,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5941,10 +5937,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>754019</v>
+        <v>753920</v>
       </c>
       <c r="R51" t="n">
-        <v>7232699</v>
+        <v>7232665</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5971,12 +5967,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Flera stycken i grupp, läten osv även synobs</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6001,21 +6012,21 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126270151</t>
+          <t>https://artportalen.se/Sighting/135183830</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126270152</v>
+        <v>135183831</v>
       </c>
       <c r="B52" t="n">
-        <v>58057</v>
+        <v>58141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6023,21 +6034,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6045,7 +6056,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6055,10 +6066,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>754023</v>
+        <v>753929</v>
       </c>
       <c r="R52" t="n">
-        <v>7232724</v>
+        <v>7232725</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6085,12 +6096,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6115,21 +6141,21 @@
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126270152</t>
+          <t>https://artportalen.se/Sighting/135183831</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126270154</v>
+        <v>135183832</v>
       </c>
       <c r="B53" t="n">
-        <v>58057</v>
+        <v>58141</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6137,21 +6163,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6159,7 +6185,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6169,10 +6195,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>754057</v>
+        <v>754077</v>
       </c>
       <c r="R53" t="n">
-        <v>7232729</v>
+        <v>7232835</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6199,12 +6225,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6229,21 +6270,21 @@
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126270154</t>
+          <t>https://artportalen.se/Sighting/135183832</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125830873</v>
+        <v>126270151</v>
       </c>
       <c r="B54" t="n">
-        <v>79917</v>
+        <v>58057</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6251,34 +6292,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Snörsmyran, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>754163</v>
+        <v>754019</v>
       </c>
       <c r="R54" t="n">
-        <v>7232822</v>
+        <v>7232699</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6305,12 +6354,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6319,7 +6368,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6340,6 +6388,341 @@
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270151</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126270152</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Snörsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>754023</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7232724</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270152</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126270154</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Snörsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>754057</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7232729</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270154</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125830873</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Snörsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>754163</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7232822</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125830873</t>
         </is>
@@ -6400,6 +6783,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -5901,7 +5901,7 @@
         <v>135183830</v>
       </c>
       <c r="B51" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>135183831</v>
       </c>
       <c r="B52" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>135183832</v>
       </c>
       <c r="B53" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -5901,7 +5901,7 @@
         <v>135183830</v>
       </c>
       <c r="B51" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>135183831</v>
       </c>
       <c r="B52" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>135183832</v>
       </c>
       <c r="B53" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -5901,7 +5901,7 @@
         <v>135183830</v>
       </c>
       <c r="B51" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>135183831</v>
       </c>
       <c r="B52" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>135183832</v>
       </c>
       <c r="B53" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -5901,7 +5901,7 @@
         <v>135183830</v>
       </c>
       <c r="B51" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>135183831</v>
       </c>
       <c r="B52" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>135183832</v>
       </c>
       <c r="B53" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 24078-2025 artfynd.xlsx
+++ b/artfynd/A 24078-2025 artfynd.xlsx
@@ -5901,7 +5901,7 @@
         <v>135183830</v>
       </c>
       <c r="B51" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>135183831</v>
       </c>
       <c r="B52" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>135183832</v>
       </c>
       <c r="B53" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
